--- a/artfynd/A 59511-2025 artfynd.xlsx
+++ b/artfynd/A 59511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688195</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688196</v>
       </c>
       <c r="B3" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59511-2025 artfynd.xlsx
+++ b/artfynd/A 59511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688195</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688196</v>
       </c>
       <c r="B3" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59511-2025 artfynd.xlsx
+++ b/artfynd/A 59511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688195</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688196</v>
       </c>
       <c r="B3" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59511-2025 artfynd.xlsx
+++ b/artfynd/A 59511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688195</v>
       </c>
       <c r="B2" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688196</v>
       </c>
       <c r="B3" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
